--- a/rank.xlsx
+++ b/rank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neven/Documents/github-repos/croatian-quiz-scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8356AC77-F1C6-D24B-8C3E-45D3D36413E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A9AAF1-096F-DA4D-B3BD-D78E6DF47F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" firstSheet="30" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" firstSheet="14" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOVA 2017" sheetId="1" r:id="rId1"/>
@@ -34,30 +34,31 @@
     <sheet name="MMM 2025" sheetId="19" r:id="rId19"/>
     <sheet name="Osijek Open 2025" sheetId="20" r:id="rId20"/>
     <sheet name="SOVA 2026" sheetId="46" r:id="rId21"/>
-    <sheet name="Croatian Open 2015" sheetId="44" r:id="rId22"/>
-    <sheet name="Croatian Open 2016" sheetId="45" r:id="rId23"/>
-    <sheet name="Croatian Open 2017" sheetId="21" r:id="rId24"/>
-    <sheet name="Croatian Open 2018" sheetId="22" r:id="rId25"/>
-    <sheet name="Croatian Open 2019" sheetId="23" r:id="rId26"/>
-    <sheet name="Croatian Open 2020" sheetId="24" r:id="rId27"/>
-    <sheet name="Croatian Open 2021" sheetId="25" r:id="rId28"/>
-    <sheet name="Croatian Open 2022" sheetId="26" r:id="rId29"/>
-    <sheet name="Croatian Open 2023" sheetId="27" r:id="rId30"/>
-    <sheet name="Croatian Open 2024" sheetId="28" r:id="rId31"/>
-    <sheet name="Croatian Open 2025" sheetId="29" r:id="rId32"/>
-    <sheet name="WQC 2014" sheetId="30" r:id="rId33"/>
-    <sheet name="WQC 2015" sheetId="31" r:id="rId34"/>
-    <sheet name="WQC 2025" sheetId="32" r:id="rId35"/>
-    <sheet name="WQC 2026" sheetId="47" r:id="rId36"/>
-    <sheet name="WQC 2024" sheetId="33" r:id="rId37"/>
-    <sheet name="WQC 2023" sheetId="34" r:id="rId38"/>
-    <sheet name="WQC 2022" sheetId="35" r:id="rId39"/>
-    <sheet name="WQC 2021" sheetId="36" r:id="rId40"/>
-    <sheet name="WQC 2020" sheetId="37" r:id="rId41"/>
-    <sheet name="WQC 2019" sheetId="38" r:id="rId42"/>
-    <sheet name="WQC 2018" sheetId="39" r:id="rId43"/>
-    <sheet name="WQC 2017" sheetId="40" r:id="rId44"/>
-    <sheet name="WQC 2016" sheetId="41" r:id="rId45"/>
+    <sheet name="MMM 2026" sheetId="48" r:id="rId22"/>
+    <sheet name="Croatian Open 2015" sheetId="44" r:id="rId23"/>
+    <sheet name="Croatian Open 2016" sheetId="45" r:id="rId24"/>
+    <sheet name="Croatian Open 2017" sheetId="21" r:id="rId25"/>
+    <sheet name="Croatian Open 2018" sheetId="22" r:id="rId26"/>
+    <sheet name="Croatian Open 2019" sheetId="23" r:id="rId27"/>
+    <sheet name="Croatian Open 2020" sheetId="24" r:id="rId28"/>
+    <sheet name="Croatian Open 2021" sheetId="25" r:id="rId29"/>
+    <sheet name="Croatian Open 2022" sheetId="26" r:id="rId30"/>
+    <sheet name="Croatian Open 2023" sheetId="27" r:id="rId31"/>
+    <sheet name="Croatian Open 2024" sheetId="28" r:id="rId32"/>
+    <sheet name="Croatian Open 2025" sheetId="29" r:id="rId33"/>
+    <sheet name="WQC 2014" sheetId="30" r:id="rId34"/>
+    <sheet name="WQC 2015" sheetId="31" r:id="rId35"/>
+    <sheet name="WQC 2025" sheetId="32" r:id="rId36"/>
+    <sheet name="WQC 2026" sheetId="47" r:id="rId37"/>
+    <sheet name="WQC 2024" sheetId="33" r:id="rId38"/>
+    <sheet name="WQC 2023" sheetId="34" r:id="rId39"/>
+    <sheet name="WQC 2022" sheetId="35" r:id="rId40"/>
+    <sheet name="WQC 2021" sheetId="36" r:id="rId41"/>
+    <sheet name="WQC 2020" sheetId="37" r:id="rId42"/>
+    <sheet name="WQC 2019" sheetId="38" r:id="rId43"/>
+    <sheet name="WQC 2018" sheetId="39" r:id="rId44"/>
+    <sheet name="WQC 2017" sheetId="40" r:id="rId45"/>
+    <sheet name="WQC 2016" sheetId="41" r:id="rId46"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4313" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="992">
   <si>
     <t>Krešimir Štimac</t>
   </si>
@@ -2974,6 +2975,84 @@
   </si>
   <si>
     <t>Sergije Michieli</t>
+  </si>
+  <si>
+    <t>George Scratcherd</t>
+  </si>
+  <si>
+    <t>Péter Lang</t>
+  </si>
+  <si>
+    <t>Tibor Kiss</t>
+  </si>
+  <si>
+    <t>Rob Sutherland</t>
+  </si>
+  <si>
+    <t>Mirta Škrlec</t>
+  </si>
+  <si>
+    <t>Ivan Požežanac-Hajić</t>
+  </si>
+  <si>
+    <t>Ákos Keresztúri</t>
+  </si>
+  <si>
+    <t>Sven Šijak</t>
+  </si>
+  <si>
+    <t>Abhinav Kishore</t>
+  </si>
+  <si>
+    <t>Mario Kolanović</t>
+  </si>
+  <si>
+    <t>Mihály Bence Bokor</t>
+  </si>
+  <si>
+    <t>Joško Puljak</t>
+  </si>
+  <si>
+    <t>Mare Knežević</t>
+  </si>
+  <si>
+    <t>Csaba Rendek</t>
+  </si>
+  <si>
+    <t>Marko Antolović</t>
+  </si>
+  <si>
+    <t>Petar Ivić</t>
+  </si>
+  <si>
+    <t>Gvido Piasevoli</t>
+  </si>
+  <si>
+    <t>Ivan Pavičić</t>
+  </si>
+  <si>
+    <t>Dario Vitas</t>
+  </si>
+  <si>
+    <t>Predrag Životić</t>
+  </si>
+  <si>
+    <t>Duje Kuzmić</t>
+  </si>
+  <si>
+    <t>Saša Sandžaktar</t>
+  </si>
+  <si>
+    <t>Kornél Patocskai-Vermes</t>
+  </si>
+  <si>
+    <t>Ádám Sugár</t>
+  </si>
+  <si>
+    <t>Zoé Kostova</t>
+  </si>
+  <si>
+    <t>Antea Barišić Vitas</t>
   </si>
 </sst>
 </file>
@@ -25105,6 +25184,2367 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98829182-AA35-514B-85F8-BB01290CBACF}">
+  <dimension ref="A1:D211"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1">
+        <v>151</v>
+      </c>
+      <c r="D1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>142</v>
+      </c>
+      <c r="D2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>140</v>
+      </c>
+      <c r="D3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>132</v>
+      </c>
+      <c r="D4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5">
+        <v>129</v>
+      </c>
+      <c r="D5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>127</v>
+      </c>
+      <c r="D6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7">
+        <v>126</v>
+      </c>
+      <c r="D7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>124</v>
+      </c>
+      <c r="D8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>121</v>
+      </c>
+      <c r="D9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>119</v>
+      </c>
+      <c r="D10">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C15">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>966</v>
+      </c>
+      <c r="C21">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>298</v>
+      </c>
+      <c r="C22">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>351</v>
+      </c>
+      <c r="C25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>967</v>
+      </c>
+      <c r="C26">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>390</v>
+      </c>
+      <c r="C28">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>505</v>
+      </c>
+      <c r="C32">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>503</v>
+      </c>
+      <c r="C33">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>316</v>
+      </c>
+      <c r="C34">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>391</v>
+      </c>
+      <c r="C35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>303</v>
+      </c>
+      <c r="C38">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>968</v>
+      </c>
+      <c r="C39">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>310</v>
+      </c>
+      <c r="C40">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>431</v>
+      </c>
+      <c r="C42">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>955</v>
+      </c>
+      <c r="C43">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>507</v>
+      </c>
+      <c r="C45">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>427</v>
+      </c>
+      <c r="C47">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>259</v>
+      </c>
+      <c r="C50">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>969</v>
+      </c>
+      <c r="C51">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>134</v>
+      </c>
+      <c r="C52">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" t="s">
+        <v>191</v>
+      </c>
+      <c r="C54">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>343</v>
+      </c>
+      <c r="C55">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>472</v>
+      </c>
+      <c r="C56">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>435</v>
+      </c>
+      <c r="C57">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>432</v>
+      </c>
+      <c r="C59">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>398</v>
+      </c>
+      <c r="C60">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>970</v>
+      </c>
+      <c r="C61">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>189</v>
+      </c>
+      <c r="C62">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>930</v>
+      </c>
+      <c r="C63">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s">
+        <v>506</v>
+      </c>
+      <c r="C65">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s">
+        <v>441</v>
+      </c>
+      <c r="C67">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" t="s">
+        <v>508</v>
+      </c>
+      <c r="C68">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>971</v>
+      </c>
+      <c r="C70">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>511</v>
+      </c>
+      <c r="C71">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>73</v>
+      </c>
+      <c r="B73" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>434</v>
+      </c>
+      <c r="C74">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>75</v>
+      </c>
+      <c r="B75" t="s">
+        <v>300</v>
+      </c>
+      <c r="C75">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>76</v>
+      </c>
+      <c r="B76" t="s">
+        <v>279</v>
+      </c>
+      <c r="C76">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>77</v>
+      </c>
+      <c r="B77" t="s">
+        <v>972</v>
+      </c>
+      <c r="C77">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>516</v>
+      </c>
+      <c r="C78">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
+        <v>438</v>
+      </c>
+      <c r="C79">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>520</v>
+      </c>
+      <c r="C80">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>81</v>
+      </c>
+      <c r="B81" t="s">
+        <v>361</v>
+      </c>
+      <c r="C81">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>280</v>
+      </c>
+      <c r="C82">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s">
+        <v>99</v>
+      </c>
+      <c r="C83">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>446</v>
+      </c>
+      <c r="C84">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>75</v>
+      </c>
+      <c r="C85">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>52</v>
+      </c>
+      <c r="C86">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>489</v>
+      </c>
+      <c r="C87">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="B90" t="s">
+        <v>519</v>
+      </c>
+      <c r="C90">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>263</v>
+      </c>
+      <c r="C92">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>93</v>
+      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>543</v>
+      </c>
+      <c r="C94">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>487</v>
+      </c>
+      <c r="C95">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>437</v>
+      </c>
+      <c r="C96">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>524</v>
+      </c>
+      <c r="C97">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>370</v>
+      </c>
+      <c r="C98">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>154</v>
+      </c>
+      <c r="C99">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>512</v>
+      </c>
+      <c r="C100">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="B101" t="s">
+        <v>409</v>
+      </c>
+      <c r="C101">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
+        <v>527</v>
+      </c>
+      <c r="C103">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>104</v>
+      </c>
+      <c r="B104" t="s">
+        <v>973</v>
+      </c>
+      <c r="C104">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>314</v>
+      </c>
+      <c r="C105">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>106</v>
+      </c>
+      <c r="B106" t="s">
+        <v>188</v>
+      </c>
+      <c r="C106">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>107</v>
+      </c>
+      <c r="B107" t="s">
+        <v>934</v>
+      </c>
+      <c r="C107">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>108</v>
+      </c>
+      <c r="B108" t="s">
+        <v>440</v>
+      </c>
+      <c r="C108">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>109</v>
+      </c>
+      <c r="B109" t="s">
+        <v>144</v>
+      </c>
+      <c r="C109">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>110</v>
+      </c>
+      <c r="B110" t="s">
+        <v>974</v>
+      </c>
+      <c r="C110">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>416</v>
+      </c>
+      <c r="C111">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>372</v>
+      </c>
+      <c r="C112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>113</v>
+      </c>
+      <c r="B113" t="s">
+        <v>151</v>
+      </c>
+      <c r="C113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>165</v>
+      </c>
+      <c r="C114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s">
+        <v>410</v>
+      </c>
+      <c r="C115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
+        <v>537</v>
+      </c>
+      <c r="C116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>117</v>
+      </c>
+      <c r="B117" t="s">
+        <v>518</v>
+      </c>
+      <c r="C117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>118</v>
+      </c>
+      <c r="B118" t="s">
+        <v>429</v>
+      </c>
+      <c r="C118">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>119</v>
+      </c>
+      <c r="B119" t="s">
+        <v>541</v>
+      </c>
+      <c r="C119">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>120</v>
+      </c>
+      <c r="B120" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>121</v>
+      </c>
+      <c r="B121" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>122</v>
+      </c>
+      <c r="B122" t="s">
+        <v>531</v>
+      </c>
+      <c r="C122">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>123</v>
+      </c>
+      <c r="B123" t="s">
+        <v>397</v>
+      </c>
+      <c r="C123">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>124</v>
+      </c>
+      <c r="B124" t="s">
+        <v>536</v>
+      </c>
+      <c r="C124">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>125</v>
+      </c>
+      <c r="B125" t="s">
+        <v>362</v>
+      </c>
+      <c r="C125">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>126</v>
+      </c>
+      <c r="B126" t="s">
+        <v>63</v>
+      </c>
+      <c r="C126">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>127</v>
+      </c>
+      <c r="B127" t="s">
+        <v>53</v>
+      </c>
+      <c r="C127">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>128</v>
+      </c>
+      <c r="B128" t="s">
+        <v>319</v>
+      </c>
+      <c r="C128">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s">
+        <v>218</v>
+      </c>
+      <c r="C129">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>234</v>
+      </c>
+      <c r="C130">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>975</v>
+      </c>
+      <c r="C131">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>132</v>
+      </c>
+      <c r="B132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>647</v>
+      </c>
+      <c r="C133">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>264</v>
+      </c>
+      <c r="C134">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>135</v>
+      </c>
+      <c r="B135" t="s">
+        <v>540</v>
+      </c>
+      <c r="C135">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>401</v>
+      </c>
+      <c r="C136">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s">
+        <v>526</v>
+      </c>
+      <c r="C137">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>138</v>
+      </c>
+      <c r="B138" t="s">
+        <v>284</v>
+      </c>
+      <c r="C138">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>139</v>
+      </c>
+      <c r="B139" t="s">
+        <v>400</v>
+      </c>
+      <c r="C139">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>140</v>
+      </c>
+      <c r="B140" t="s">
+        <v>110</v>
+      </c>
+      <c r="C140">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>141</v>
+      </c>
+      <c r="B141" t="s">
+        <v>474</v>
+      </c>
+      <c r="C141">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>142</v>
+      </c>
+      <c r="B142" t="s">
+        <v>976</v>
+      </c>
+      <c r="C142">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>143</v>
+      </c>
+      <c r="B143" t="s">
+        <v>521</v>
+      </c>
+      <c r="C143">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>144</v>
+      </c>
+      <c r="B144" t="s">
+        <v>977</v>
+      </c>
+      <c r="C144">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>145</v>
+      </c>
+      <c r="B145" t="s">
+        <v>433</v>
+      </c>
+      <c r="C145">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>146</v>
+      </c>
+      <c r="B146" t="s">
+        <v>517</v>
+      </c>
+      <c r="C146">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>147</v>
+      </c>
+      <c r="B147" t="s">
+        <v>79</v>
+      </c>
+      <c r="C147">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>148</v>
+      </c>
+      <c r="B148" t="s">
+        <v>404</v>
+      </c>
+      <c r="C148">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>149</v>
+      </c>
+      <c r="B149" t="s">
+        <v>408</v>
+      </c>
+      <c r="C149">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>150</v>
+      </c>
+      <c r="B150" t="s">
+        <v>663</v>
+      </c>
+      <c r="C150">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>151</v>
+      </c>
+      <c r="B151" t="s">
+        <v>358</v>
+      </c>
+      <c r="C151">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>152</v>
+      </c>
+      <c r="B152" t="s">
+        <v>733</v>
+      </c>
+      <c r="C152">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>153</v>
+      </c>
+      <c r="B153" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>154</v>
+      </c>
+      <c r="B154" t="s">
+        <v>459</v>
+      </c>
+      <c r="C154">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>364</v>
+      </c>
+      <c r="C155">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>156</v>
+      </c>
+      <c r="B156" t="s">
+        <v>525</v>
+      </c>
+      <c r="C156">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>157</v>
+      </c>
+      <c r="B157" t="s">
+        <v>104</v>
+      </c>
+      <c r="C157">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>158</v>
+      </c>
+      <c r="B158" t="s">
+        <v>443</v>
+      </c>
+      <c r="C158">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>159</v>
+      </c>
+      <c r="B159" t="s">
+        <v>419</v>
+      </c>
+      <c r="C159">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>160</v>
+      </c>
+      <c r="B160" t="s">
+        <v>411</v>
+      </c>
+      <c r="C160">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>161</v>
+      </c>
+      <c r="B161" t="s">
+        <v>208</v>
+      </c>
+      <c r="C161">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>162</v>
+      </c>
+      <c r="B162" t="s">
+        <v>374</v>
+      </c>
+      <c r="C162">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>163</v>
+      </c>
+      <c r="B163" t="s">
+        <v>367</v>
+      </c>
+      <c r="C163">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>164</v>
+      </c>
+      <c r="B164" t="s">
+        <v>168</v>
+      </c>
+      <c r="C164">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>165</v>
+      </c>
+      <c r="B165" t="s">
+        <v>978</v>
+      </c>
+      <c r="C165">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>166</v>
+      </c>
+      <c r="B166" t="s">
+        <v>979</v>
+      </c>
+      <c r="C166">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>167</v>
+      </c>
+      <c r="B167" t="s">
+        <v>562</v>
+      </c>
+      <c r="C167">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>168</v>
+      </c>
+      <c r="B168" t="s">
+        <v>115</v>
+      </c>
+      <c r="C168">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>169</v>
+      </c>
+      <c r="B169" t="s">
+        <v>980</v>
+      </c>
+      <c r="C169">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>170</v>
+      </c>
+      <c r="B170" t="s">
+        <v>451</v>
+      </c>
+      <c r="C170">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>171</v>
+      </c>
+      <c r="B171" t="s">
+        <v>940</v>
+      </c>
+      <c r="C171">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>172</v>
+      </c>
+      <c r="B172" t="s">
+        <v>981</v>
+      </c>
+      <c r="C172">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>173</v>
+      </c>
+      <c r="B173" t="s">
+        <v>553</v>
+      </c>
+      <c r="C173">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>174</v>
+      </c>
+      <c r="B174" t="s">
+        <v>677</v>
+      </c>
+      <c r="C174">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>175</v>
+      </c>
+      <c r="B175" t="s">
+        <v>982</v>
+      </c>
+      <c r="C175">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>176</v>
+      </c>
+      <c r="B176" t="s">
+        <v>377</v>
+      </c>
+      <c r="C176">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>177</v>
+      </c>
+      <c r="B177" t="s">
+        <v>606</v>
+      </c>
+      <c r="C177">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>178</v>
+      </c>
+      <c r="B178" t="s">
+        <v>289</v>
+      </c>
+      <c r="C178">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>179</v>
+      </c>
+      <c r="B179" t="s">
+        <v>122</v>
+      </c>
+      <c r="C179">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>180</v>
+      </c>
+      <c r="B180" t="s">
+        <v>564</v>
+      </c>
+      <c r="C180">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>181</v>
+      </c>
+      <c r="B181" t="s">
+        <v>547</v>
+      </c>
+      <c r="C181">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>182</v>
+      </c>
+      <c r="B182" t="s">
+        <v>456</v>
+      </c>
+      <c r="C182">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>183</v>
+      </c>
+      <c r="B183" t="s">
+        <v>287</v>
+      </c>
+      <c r="C183">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>184</v>
+      </c>
+      <c r="B184" t="s">
+        <v>550</v>
+      </c>
+      <c r="C184">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>185</v>
+      </c>
+      <c r="B185" t="s">
+        <v>546</v>
+      </c>
+      <c r="C185">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>186</v>
+      </c>
+      <c r="B186" t="s">
+        <v>418</v>
+      </c>
+      <c r="C186">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>187</v>
+      </c>
+      <c r="B187" t="s">
+        <v>217</v>
+      </c>
+      <c r="C187">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>188</v>
+      </c>
+      <c r="B188" t="s">
+        <v>494</v>
+      </c>
+      <c r="C188">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>189</v>
+      </c>
+      <c r="B189" t="s">
+        <v>482</v>
+      </c>
+      <c r="C189">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>190</v>
+      </c>
+      <c r="B190" t="s">
+        <v>983</v>
+      </c>
+      <c r="C190">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>191</v>
+      </c>
+      <c r="B191" t="s">
+        <v>335</v>
+      </c>
+      <c r="C191">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>192</v>
+      </c>
+      <c r="B192" t="s">
+        <v>78</v>
+      </c>
+      <c r="C192">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>193</v>
+      </c>
+      <c r="B193" t="s">
+        <v>36</v>
+      </c>
+      <c r="C193">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>194</v>
+      </c>
+      <c r="B194" t="s">
+        <v>984</v>
+      </c>
+      <c r="C194">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>195</v>
+      </c>
+      <c r="B195" t="s">
+        <v>985</v>
+      </c>
+      <c r="C195">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>196</v>
+      </c>
+      <c r="B196" t="s">
+        <v>986</v>
+      </c>
+      <c r="C196">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>197</v>
+      </c>
+      <c r="B197" t="s">
+        <v>462</v>
+      </c>
+      <c r="C197">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>198</v>
+      </c>
+      <c r="B198" t="s">
+        <v>987</v>
+      </c>
+      <c r="C198">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>199</v>
+      </c>
+      <c r="B199" t="s">
+        <v>988</v>
+      </c>
+      <c r="C199">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>200</v>
+      </c>
+      <c r="B200" t="s">
+        <v>989</v>
+      </c>
+      <c r="C200">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>201</v>
+      </c>
+      <c r="B201" t="s">
+        <v>465</v>
+      </c>
+      <c r="C201">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>202</v>
+      </c>
+      <c r="B202" t="s">
+        <v>420</v>
+      </c>
+      <c r="C202">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>203</v>
+      </c>
+      <c r="B203" t="s">
+        <v>468</v>
+      </c>
+      <c r="C203">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>204</v>
+      </c>
+      <c r="B204" t="s">
+        <v>554</v>
+      </c>
+      <c r="C204">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>205</v>
+      </c>
+      <c r="B205" t="s">
+        <v>94</v>
+      </c>
+      <c r="C205">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>206</v>
+      </c>
+      <c r="B206" t="s">
+        <v>990</v>
+      </c>
+      <c r="C206">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>207</v>
+      </c>
+      <c r="B207" t="s">
+        <v>991</v>
+      </c>
+      <c r="C207">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>208</v>
+      </c>
+      <c r="B208" t="s">
+        <v>58</v>
+      </c>
+      <c r="C208">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>209</v>
+      </c>
+      <c r="B209" t="s">
+        <v>743</v>
+      </c>
+      <c r="C209">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>210</v>
+      </c>
+      <c r="B210" t="s">
+        <v>532</v>
+      </c>
+      <c r="C210">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>211</v>
+      </c>
+      <c r="B211" t="s">
+        <v>387</v>
+      </c>
+      <c r="C211">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F7F02A-6B68-0C4F-B03E-012278D8BB25}">
   <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -25719,7 +28159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF51EAFD-3809-A74B-B55F-B64F3DA7F7E5}">
   <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -26554,7 +28994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -27448,7 +29888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -28494,7 +30934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -29498,7 +31938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -30711,7 +33151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -31873,823 +34313,6 @@
       </c>
       <c r="C105" s="2">
         <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:C73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="10.83203125" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="2">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="C2" s="2">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" s="2">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="C9" s="2">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="2">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="2">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C14" s="2">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="2">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C17" s="2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="2">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="2">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C21" s="2">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C22" s="2">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C25" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="2">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="C28" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C29" s="2">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C30" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>31</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>32</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C32" s="2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>34</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
-        <v>35</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C35" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>36</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="C36" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
-        <v>37</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C37" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
-        <v>38</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C38" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>39</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>40</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C40" s="2">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>41</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C41" s="2">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
-        <v>42</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C42" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="2">
-        <v>43</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="2">
-        <v>44</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C44" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="2">
-        <v>45</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C45" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="2">
-        <v>46</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="2">
-        <v>47</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C47" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="2">
-        <v>48</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C48" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="2">
-        <v>49</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C49" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="2">
-        <v>50</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C50" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="2">
-        <v>51</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C51" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="2">
-        <v>52</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C52" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="2">
-        <v>53</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C53" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="2">
-        <v>54</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C54" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="2">
-        <v>55</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="2">
-        <v>56</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C56" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="2">
-        <v>57</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="2">
-        <v>58</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="2">
-        <v>59</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="2">
-        <v>60</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C60" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="2">
-        <v>61</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C61" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="2">
-        <v>62</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C62" s="2">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="2">
-        <v>63</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C63" s="2">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="2">
-        <v>64</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C64" s="2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="2">
-        <v>65</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C65" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="2">
-        <v>66</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C66" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="2">
-        <v>67</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C67" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="2">
-        <v>68</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C68" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="2">
-        <v>69</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="C69" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="2">
-        <v>70</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C70" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="2">
-        <v>71</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C71" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="2">
-        <v>72</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C72" s="2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="2">
-        <v>73</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C73" s="2">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -33638,6 +35261,823 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+  <dimension ref="A1:C73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C2" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C9" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C25" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C28" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C29" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C30" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C31" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C35" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C36" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C38" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>39</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C40" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C41" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C42" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>44</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C44" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C45" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C47" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C48" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C49" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C50" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C52" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C53" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C54" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>55</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C56" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>59</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C60" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C61" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>63</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C63" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>64</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C64" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>65</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>66</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C66" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C67" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>69</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C69" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C71" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C73" s="2">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -34432,7 +36872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -35574,7 +38014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -36446,7 +38886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -37032,7 +39472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -37739,7 +40179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -38875,7 +41315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48222230-6720-4C49-9F89-FD6BE3B5DBF5}">
   <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -40054,7 +42494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -41026,7 +43466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -42056,1021 +44496,6 @@
       </c>
       <c r="C93" s="3">
         <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
-  <dimension ref="A1:C91"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="8.83203125" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="3">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="3">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" s="3">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C8" s="3">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="3">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C14" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>15</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C16" s="3">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="3">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>18</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>19</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C19" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="3">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="3">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="3">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C25" s="3">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
-        <v>26</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="C26" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
-        <v>27</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C27" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
-        <v>28</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="3">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>29</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="3">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="3">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>31</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C31" s="3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>32</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C32" s="3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>33</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C33" s="3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
-        <v>34</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>35</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C35" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
-        <v>36</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C36" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C38" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="3">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C41" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="C42" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
-        <v>43</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
-        <v>44</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C44" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>45</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C45" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>46</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C46" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <v>47</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C47" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
-        <v>48</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C48" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
-        <v>49</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C49" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C50" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
-        <v>51</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C51" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
-        <v>52</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C52" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
-        <v>53</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C53" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
-        <v>54</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="C54" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
-        <v>55</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C55" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
-        <v>56</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
-        <v>57</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C57" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
-        <v>58</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C58" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
-        <v>59</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C59" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
-        <v>60</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C60" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
-        <v>61</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
-        <v>62</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C62" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
-        <v>63</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C63" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
-        <v>64</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C64" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
-        <v>65</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C65" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
-        <v>66</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C66" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
-        <v>67</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C67" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
-        <v>68</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="C68" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
-        <v>69</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="C69" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
-        <v>70</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="C70" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
-        <v>71</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C71" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
-        <v>72</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="C72" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
-        <v>73</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="C73" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
-        <v>74</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="C74" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
-        <v>75</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="C75" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
-        <v>76</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
-        <v>77</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
-        <v>78</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C78" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
-        <v>79</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="C79" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
-        <v>80</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C80" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
-        <v>81</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="C81" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>82</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="C82" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
-        <v>83</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C83" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
-        <v>84</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C84" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
-        <v>85</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C85" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
-        <v>86</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="C86" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
-        <v>87</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C87" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
-        <v>88</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="C88" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
-        <v>89</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C89" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>90</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C90" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
-        <v>91</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C91" s="3">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -45293,6 +46718,1021 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
+  <dimension ref="A1:C91"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="8.83203125" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="3">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C8" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C26" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>33</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C35" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C36" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C41" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="C42" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>43</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>44</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>45</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>46</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C46" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>47</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C47" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>48</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>49</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C50" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>51</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C51" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>53</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C53" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C54" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>55</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>56</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>57</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C57" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>58</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C58" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <v>59</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C59" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <v>60</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C60" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <v>61</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <v>62</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C62" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>63</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>64</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C64" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <v>65</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <v>66</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C66" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>67</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C67" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>68</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C68" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>69</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C69" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>70</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C70" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>71</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <v>72</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="C72" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>73</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C73" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>74</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C74" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>75</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C75" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>76</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>77</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>78</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C78" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>79</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C79" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <v>80</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C80" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>81</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C81" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>82</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C82" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>83</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C83" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>84</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C84" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>85</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C85" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>86</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C86" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>87</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <v>88</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="C88" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="3">
+        <v>89</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C89" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <v>90</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C90" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="3">
+        <v>91</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C91" s="3">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -46615,7 +49055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -47531,7 +49971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -49448,7 +51888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -51662,7 +54102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -52974,7 +55414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/rank.xlsx
+++ b/rank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neven/Documents/github-repos/croatian-quiz-scores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A9AAF1-096F-DA4D-B3BD-D78E6DF47F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A742A9-390B-CA48-9403-5F7E31D941A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" firstSheet="14" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15620" firstSheet="27" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOVA 2017" sheetId="1" r:id="rId1"/>
@@ -46,19 +46,20 @@
     <sheet name="Croatian Open 2023" sheetId="27" r:id="rId31"/>
     <sheet name="Croatian Open 2024" sheetId="28" r:id="rId32"/>
     <sheet name="Croatian Open 2025" sheetId="29" r:id="rId33"/>
-    <sheet name="WQC 2014" sheetId="30" r:id="rId34"/>
-    <sheet name="WQC 2015" sheetId="31" r:id="rId35"/>
-    <sheet name="WQC 2025" sheetId="32" r:id="rId36"/>
-    <sheet name="WQC 2026" sheetId="47" r:id="rId37"/>
-    <sheet name="WQC 2024" sheetId="33" r:id="rId38"/>
-    <sheet name="WQC 2023" sheetId="34" r:id="rId39"/>
-    <sheet name="WQC 2022" sheetId="35" r:id="rId40"/>
-    <sheet name="WQC 2021" sheetId="36" r:id="rId41"/>
-    <sheet name="WQC 2020" sheetId="37" r:id="rId42"/>
-    <sheet name="WQC 2019" sheetId="38" r:id="rId43"/>
-    <sheet name="WQC 2018" sheetId="39" r:id="rId44"/>
-    <sheet name="WQC 2017" sheetId="40" r:id="rId45"/>
-    <sheet name="WQC 2016" sheetId="41" r:id="rId46"/>
+    <sheet name="Croatian Open 2026" sheetId="49" r:id="rId34"/>
+    <sheet name="WQC 2014" sheetId="30" r:id="rId35"/>
+    <sheet name="WQC 2015" sheetId="31" r:id="rId36"/>
+    <sheet name="WQC 2025" sheetId="32" r:id="rId37"/>
+    <sheet name="WQC 2026" sheetId="47" r:id="rId38"/>
+    <sheet name="WQC 2024" sheetId="33" r:id="rId39"/>
+    <sheet name="WQC 2023" sheetId="34" r:id="rId40"/>
+    <sheet name="WQC 2022" sheetId="35" r:id="rId41"/>
+    <sheet name="WQC 2021" sheetId="36" r:id="rId42"/>
+    <sheet name="WQC 2020" sheetId="37" r:id="rId43"/>
+    <sheet name="WQC 2019" sheetId="38" r:id="rId44"/>
+    <sheet name="WQC 2018" sheetId="39" r:id="rId45"/>
+    <sheet name="WQC 2017" sheetId="40" r:id="rId46"/>
+    <sheet name="WQC 2016" sheetId="41" r:id="rId47"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4624" uniqueCount="997">
   <si>
     <t>Krešimir Štimac</t>
   </si>
@@ -3053,6 +3054,21 @@
   </si>
   <si>
     <t>Antea Barišić Vitas</t>
+  </si>
+  <si>
+    <t>Marko Janković</t>
+  </si>
+  <si>
+    <t>Andrija Golub</t>
+  </si>
+  <si>
+    <t>Karlo Vrban</t>
+  </si>
+  <si>
+    <t>Krešimir Krpan</t>
+  </si>
+  <si>
+    <t>Bruno Klišmanić</t>
   </si>
 </sst>
 </file>
@@ -38887,6 +38903,1116 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6D2654-55D0-9D47-B244-5934A60862FB}">
+  <dimension ref="A1:C100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C10">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>955</v>
+      </c>
+      <c r="C11">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>382</v>
+      </c>
+      <c r="C13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>659</v>
+      </c>
+      <c r="C16">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C19">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>353</v>
+      </c>
+      <c r="C28">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>647</v>
+      </c>
+      <c r="C31">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>441</v>
+      </c>
+      <c r="C33">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>398</v>
+      </c>
+      <c r="C35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>432</v>
+      </c>
+      <c r="C36">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>674</v>
+      </c>
+      <c r="C37">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>615</v>
+      </c>
+      <c r="C38">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>556</v>
+      </c>
+      <c r="C39">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>237</v>
+      </c>
+      <c r="C40">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>472</v>
+      </c>
+      <c r="C41">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>284</v>
+      </c>
+      <c r="C42">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>956</v>
+      </c>
+      <c r="C43">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>673</v>
+      </c>
+      <c r="C44">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>489</v>
+      </c>
+      <c r="C46">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>306</v>
+      </c>
+      <c r="C47">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>512</v>
+      </c>
+      <c r="C49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>558</v>
+      </c>
+      <c r="C51">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>514</v>
+      </c>
+      <c r="C53">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>218</v>
+      </c>
+      <c r="C54">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>191</v>
+      </c>
+      <c r="C55">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>435</v>
+      </c>
+      <c r="C56">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>280</v>
+      </c>
+      <c r="C58">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>440</v>
+      </c>
+      <c r="C62">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C63">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>433</v>
+      </c>
+      <c r="C64">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s">
+        <v>559</v>
+      </c>
+      <c r="C65">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>484</v>
+      </c>
+      <c r="C67">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" t="s">
+        <v>992</v>
+      </c>
+      <c r="C68">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>438</v>
+      </c>
+      <c r="C69">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>480</v>
+      </c>
+      <c r="C71">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>993</v>
+      </c>
+      <c r="C72">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>73</v>
+      </c>
+      <c r="B73" t="s">
+        <v>527</v>
+      </c>
+      <c r="C73">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>487</v>
+      </c>
+      <c r="C74">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>75</v>
+      </c>
+      <c r="B75" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>76</v>
+      </c>
+      <c r="B76" t="s">
+        <v>653</v>
+      </c>
+      <c r="C76">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>935</v>
+      </c>
+      <c r="C77">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79" t="s">
+        <v>104</v>
+      </c>
+      <c r="C79">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>677</v>
+      </c>
+      <c r="C80">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>567</v>
+      </c>
+      <c r="C81">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>537</v>
+      </c>
+      <c r="C82">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s">
+        <v>676</v>
+      </c>
+      <c r="C83">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>453</v>
+      </c>
+      <c r="C85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>958</v>
+      </c>
+      <c r="C87">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>364</v>
+      </c>
+      <c r="C88">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>735</v>
+      </c>
+      <c r="C89">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>358</v>
+      </c>
+      <c r="C90">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>562</v>
+      </c>
+      <c r="C91">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>348</v>
+      </c>
+      <c r="C93">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>994</v>
+      </c>
+      <c r="C94">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>652</v>
+      </c>
+      <c r="C95">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>995</v>
+      </c>
+      <c r="C96">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>666</v>
+      </c>
+      <c r="C98">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>321</v>
+      </c>
+      <c r="C99">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>996</v>
+      </c>
+      <c r="C100">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -39472,7 +40598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -40179,7 +41305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -41315,7 +42441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48222230-6720-4C49-9F89-FD6BE3B5DBF5}">
   <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -42494,7 +43620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -43459,1043 +44585,6 @@
       </c>
       <c r="C87" s="3">
         <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
-  <dimension ref="A1:C93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="8.83203125" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="3">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C5" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="C8" s="3">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="3">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="3">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C14" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>15</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C15" s="3">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="3">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>17</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C17" s="3">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>18</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="C18" s="3">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>19</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C19" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="3">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C22" s="3">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="C23" s="3">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="3">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C25" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
-        <v>26</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
-        <v>27</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
-        <v>28</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C28" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>29</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C30" s="3">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>31</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>32</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>33</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
-        <v>34</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C34" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>35</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="3">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
-        <v>36</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="C36" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="C37" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C39" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C40" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C41" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C42" s="3">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
-        <v>43</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C43" s="3">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
-        <v>44</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>45</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="C45" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>46</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="C46" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <v>47</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="C47" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
-        <v>48</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="C48" s="3">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
-        <v>49</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C49" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="C50" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
-        <v>51</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="C51" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
-        <v>52</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="C52" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
-        <v>53</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C53" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
-        <v>54</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="C54" s="3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
-        <v>55</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="C55" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
-        <v>56</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C56" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
-        <v>57</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="C57" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
-        <v>58</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="C58" s="3">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
-        <v>59</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="C59" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
-        <v>60</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="C60" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
-        <v>61</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="C61" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
-        <v>62</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="C62" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
-        <v>63</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C63" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
-        <v>64</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="C64" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
-        <v>65</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C65" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
-        <v>66</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="C66" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
-        <v>67</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="3">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
-        <v>68</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="C68" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
-        <v>69</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="C69" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
-        <v>70</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C70" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
-        <v>71</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C71" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
-        <v>72</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
-        <v>73</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="C73" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
-        <v>74</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C74" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
-        <v>75</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="C75" s="3">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
-        <v>76</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="C76" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
-        <v>77</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="C77" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
-        <v>78</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C78" s="3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
-        <v>79</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="C79" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
-        <v>80</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="C80" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
-        <v>81</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="C81" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>82</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C82" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
-        <v>83</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C83" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
-        <v>84</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="C84" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
-        <v>85</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C85" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
-        <v>86</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="C86" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
-        <v>87</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C87" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
-        <v>88</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="C88" s="3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
-        <v>89</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="C89" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>90</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C90" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
-        <v>91</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="C91" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
-        <v>92</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="C92" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
-        <v>93</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C93" s="3">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -46718,6 +46807,1043 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
+  <dimension ref="A1:C93"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="8.83203125" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="3">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C5" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C8" s="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C15" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C18" s="3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>22</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C23" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C25" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C28" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C30" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>33</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C34" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C36" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C37" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C40" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C41" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C42" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>43</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C43" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>44</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>45</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C45" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>46</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="C46" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>47</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="C47" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>48</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C48" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>49</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C49" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>50</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C50" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>51</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="C51" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>52</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="C52" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>53</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C54" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>55</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C55" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>56</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>57</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C57" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>58</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="C58" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <v>59</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C59" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <v>60</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C60" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <v>61</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C61" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <v>62</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C62" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>63</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C63" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>64</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C64" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <v>65</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C65" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <v>66</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C66" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>67</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>68</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C68" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>69</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C69" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>70</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C70" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>71</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C71" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <v>72</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>73</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C73" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>74</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C74" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>75</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="C75" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>76</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C76" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>77</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C77" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>78</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C78" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>79</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C79" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <v>80</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="C80" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>81</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C81" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>82</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C82" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>83</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>84</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C84" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>85</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>86</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="C86" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>87</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C87" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <v>88</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C88" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="3">
+        <v>89</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C89" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <v>90</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C90" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="3">
+        <v>91</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C91" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="3">
+        <v>92</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="C92" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="3">
+        <v>93</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C93" s="3">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -47732,7 +48858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -49055,7 +50181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -49971,7 +51097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -51888,7 +53014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -54102,7 +55228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -55414,7 +56540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
